--- a/帝国时代2决定版 文明联盟 弩车流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 弩车流最优研究顺序 By RemonBo.xlsx
@@ -1314,242 +1314,242 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>双箭弩（重弩战象/蝎式弩可多发一枚弩箭）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>蝎式弩射程 +1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>射程提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>双箭弩（重弩战象/蝎式弩可多发一枚弩箭）</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>配重块（巨型投石机/投石车系攻+15%）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>直接强化蝎式弩</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>蝎式弩射程 +1</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>攻城武器攻速+25%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>凯尔特狂暴（攻城武器生命+40%）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>攻城武器厂的生产速度 +20%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>研究/生产速度提升，科技与产能来得更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>射程提升</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>中国</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>萨拉森</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>配重块（巨型投石机/投石车系攻+15%）</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>凯尔特</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>攻城武器攻速+25%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>攻速提升，直接抬高输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>凯尔特</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>凯尔特狂暴（攻城武器生命+40%）</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>凯尔特</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>攻城武器厂的生产速度 +20%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>攻城武器的视野 +2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>直接强化蝎式弩</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>射程提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>攻城武器的视野 +2</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
           <t>视野提升</t>
@@ -1557,9 +1557,9 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>直接强化蝎式弩</t>
+          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -1818,14 +1818,14 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1845,14 +1845,14 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>

--- a/帝国时代2决定版 文明联盟 弩车流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 弩车流最优研究顺序 By RemonBo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开局3免费位" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续2000金顺序" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甲类·蝎式弩本体强化" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·费用与前置" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·减费用与资源效率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="与弩车流无关·可跳过" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主选文明推荐" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全62文明总名次" sheetId="7" state="visible" r:id="rId7"/>
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·蝎式弩本体强化'!$A$1:$E$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·蝎式弩本体强化'!$A$1:$E$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·蝎式弩本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与弩车流无关·可跳过'!$A$1:$D$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与弩车流无关·可跳过'!$A$1:$D$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与弩车流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
@@ -584,11 +584,11 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；蝎式弩科技树 9/9（无缺项）；最直接一条：蝎式弩黄金-50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；蝎式弩科技树 9/9（无缺项）；最直接一条：蝎式弩黄金-50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -598,11 +598,11 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、建筑学</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、建筑学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+          <t>备选：阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -640,11 +640,11 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；蝎式弩科技树 9/9（无缺项）；最直接一条：双箭弩（重弩战象/蝎式弩可多发一枚弩箭）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；蝎式弩科技树 9/9（无缺项）；最直接一条：双箭弩（重弩战象/蝎式弩可多发一枚弩箭）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -654,11 +654,11 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 建筑学、工兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 建筑学、工兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
+          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
         </is>
       </c>
     </row>
@@ -696,35 +696,35 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；蝎式弩科技树 8/9；缺 攻城工程技师；最直接一条：火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；蝎式弩科技树 8/9；缺 攻城工程技师；最直接一条：火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>保加利亚（备选）</t>
+          <t>蒙古（备选）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>蒙古（备选）</t>
+          <t>蜀（备选）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、蝎式弩</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -789,7 +789,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>4</v>
       </c>
@@ -815,7 +815,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、建筑学</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、建筑学</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -875,11 +875,11 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 建筑学、工兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 建筑学、工兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>7</v>
       </c>
@@ -905,17 +905,17 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
+          <t>操练（攻城武器厂单位移速+50%）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -935,17 +935,17 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -955,27 +955,27 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>操练（攻城武器厂单位移速+50%）</t>
+          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、蝎式弩</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>攻城武器厂单位费用-15%</t>
+          <t>攻城武器木材-33%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -995,17 +995,17 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 攻城工程技师、建筑学、工兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1015,17 +1015,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
+          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>封建时代起</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、蝎式弩</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 重型蝎式弩、攻城工程技师、建筑学</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>攻城武器木材-33%</t>
+          <t>骑兵对攻城武器的攻击力 +2</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 攻城工程技师、建筑学、工兵</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 攻城工程技师、建筑学、工兵</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
+          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>封建时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 重型蝎式弩、攻城工程技师、建筑学</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 化学、弹道学、工兵</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1105,27 +1105,27 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>骑兵对攻城武器的攻击力 +2</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 攻城工程技师、建筑学、工兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；蝎式弩科技树 8/9；缺 攻城工程技师</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
+          <t>重装甲（攻城武器近战护甲+4）</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 化学、弹道学、工兵</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1165,27 +1165,27 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；蝎式弩科技树 8/9；缺 攻城工程技师</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>重装甲（攻城武器近战护甲+4）</t>
+          <t>攻城武器厂单位费用-15%</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1205,12 +1205,42 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；蝎式弩科技树 8/9；缺 重型蝎式弩</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F15"/>
+  <autoFilter ref="A1:F16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1222,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1272,17 +1302,17 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
+          <t>蝎式弩黄金-50%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -1299,17 +1329,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>降低蝎式弩的最小射程</t>
+          <t>弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -1321,22 +1351,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>双箭弩（重弩战象/蝎式弩可多发一枚弩箭）</t>
+          <t>降低蝎式弩的最小射程</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
+          <t>射程提升</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1383,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>蝎式弩射程 +1</t>
+          <t>双箭弩（重弩战象/蝎式弩可多发一枚弩箭）</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
         </is>
       </c>
     </row>
@@ -1375,39 +1405,39 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>蝎式弩射程 +1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>射程提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>中国</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>萨拉森</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>配重块（巨型投石机/投石车系攻+15%）</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1429,22 +1459,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>攻城武器攻速+25%</t>
+          <t>配重块（巨型投石机/投石车系攻+15%）</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -1461,17 +1491,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>凯尔特狂暴（攻城武器生命+40%）</t>
+          <t>攻城武器攻速+25%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -1488,44 +1518,44 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
+          <t>凯尔特狂暴（攻城武器生命+40%）</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
           <t>攻城武器厂的生产速度 +20%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>研究/生产速度提升，科技与产能来得更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>射程提升</t>
         </is>
       </c>
     </row>
@@ -1542,125 +1572,125 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
+          <t>兵营/攻城武器厂黄金升级-66%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>射程提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
           <t>攻城武器的视野 +2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>视野提升</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>埃塞俄比亚</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>扭绞机（攻城武器厂单位爆炸伤害范围提升）</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>爆炸/溅射范围提升</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>蒙古</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>操练（攻城武器厂单位移速+50%）</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>库曼</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
@@ -1672,22 +1702,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>骑兵对攻城武器的攻击力 +2</t>
+          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>机动性提升</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1729,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
+          <t>攻城武器木材-33%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1714,7 +1744,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -1726,27 +1756,135 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>骑兵对攻城武器的攻击力 +2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>马其顿人</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>减少受到的伤害，正面更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>条顿</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>重装甲（攻城武器近战护甲+4）</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E19"/>
+  <autoFilter ref="A1:E23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1758,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1796,19 +1934,19 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>蝎式弩黄金-50%</t>
+          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1823,19 +1961,19 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>兵营/攻城武器厂黄金升级-66%</t>
+          <t>攻城武器厂单位费用-15%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1850,19 +1988,19 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1876,62 +2014,8 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>攻城武器厂单位费用-15%</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>攻城武器木材-33%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:E4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1943,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2461,12 +2545,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>海军和火药文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2476,19 +2560,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牧场取代农田」）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵和骆驼文明</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2498,19 +2582,19 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牧场取代农田」）</t>
+          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局2果树丛」）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2520,19 +2604,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局2果树丛」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2542,19 +2626,19 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>弓兵与步兵文明</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2564,19 +2648,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局每种资源+25」）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明</t>
+          <t>火药文明</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2586,19 +2670,19 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局每种资源+25」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>火药文明</t>
+          <t>骑兵和海军文明</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2608,19 +2692,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2630,14 +2714,14 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2652,19 +2736,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「独轮推车/手推车免费」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2674,19 +2758,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2696,19 +2780,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2718,19 +2802,19 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「初始石料+100」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2740,19 +2824,19 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>弓兵和海军文明</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2762,19 +2846,19 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>弓兵和海军文明</t>
+          <t>骆驼和火药文明</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2784,19 +2868,19 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代费用-15%」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2806,19 +2890,19 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「房屋/聚落人口+5」）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>弓兵文明</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2828,19 +2912,19 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「房屋/聚落人口+5」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局显示敌方TC」）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>弓兵文明</t>
+          <t>弓兵和骑兵文明</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2850,19 +2934,19 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局显示敌方TC」）</t>
+          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「造船厂工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明</t>
+          <t>弓兵和象兵文明</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2872,19 +2956,19 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「造船厂工作速度+15%」）</t>
+          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采石村民缓慢获食」）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2894,14 +2978,14 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采石村民缓慢获食」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2916,19 +3000,19 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2938,34 +3022,12 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="36" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>步兵和海军文明</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强蝎式弩</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D46"/>
+  <autoFilter ref="A1:D45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3195,22 +3257,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
+          <t>操练（攻城武器厂单位移速+50%）</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 9/9。科技树无缺项</t>
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 8/9。缺：建筑学</t>
         </is>
       </c>
     </row>
@@ -3220,22 +3282,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>操练（攻城武器厂单位移速+50%）</t>
+          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 8/9。缺：建筑学</t>
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 7/9。缺：重型蝎式弩、蝎式弩</t>
         </is>
       </c>
     </row>
@@ -3245,47 +3307,47 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>攻城武器厂单位费用-15%</t>
+          <t>攻城武器木材-33%</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 8/9。缺：建筑学</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 6/9。缺：攻城工程技师、建筑学、工兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
+          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 7/9。缺：重型蝎式弩、蝎式弩</t>
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 6/9。缺：重型蝎式弩、攻城工程技师、建筑学</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3357,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3305,7 +3367,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>攻城武器木材-33%</t>
+          <t>骑兵对攻城武器的攻击力 +2</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -3314,13 +3376,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3330,12 +3392,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
+          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 6/9。缺：重型蝎式弩、攻城工程技师、建筑学</t>
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 6/9。缺：化学、弹道学、工兵</t>
         </is>
       </c>
     </row>
@@ -3345,22 +3407,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>骑兵对攻城武器的攻击力 +2</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 6/9。缺：攻城工程技师、建筑学、工兵</t>
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 8/9。缺：攻城工程技师</t>
         </is>
       </c>
     </row>
@@ -3370,22 +3432,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
+          <t>重装甲（攻城武器近战护甲+4）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 6/9。缺：化学、弹道学、工兵</t>
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 8/9。缺：建筑学</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3533,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；蝎式弩科技树 9/9（无缺项）；最直接一条：蝎式弩黄金-50%</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；蝎式弩科技树 9/9（无缺项）；最直接一条：蝎式弩黄金-50%</t>
         </is>
       </c>
     </row>
@@ -3501,11 +3563,11 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；蝎式弩科技树 9/9（无缺项）；最直接一条：双箭弩（重弩战象/蝎式弩可多发一枚弩箭）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；蝎式弩科技树 9/9（无缺项）；最直接一条：双箭弩（重弩战象/蝎式弩可多发一枚弩箭）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -3531,11 +3593,11 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；蝎式弩科技树 8/9；缺 攻城工程技师；最直接一条：火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；蝎式弩科技树 8/9；缺 攻城工程技师；最直接一条：火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -3561,7 +3623,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、建筑学</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、建筑学</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3653,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -3621,11 +3683,11 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 建筑学、工兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 建筑学、工兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -3651,17 +3713,17 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3676,22 +3738,22 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
+          <t>操练（攻城武器厂单位移速+50%）</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -3706,22 +3768,22 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>操练（攻城武器厂单位移速+50%）</t>
+          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、蝎式弩</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -3736,22 +3798,22 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>攻城武器厂单位费用-15%</t>
+          <t>攻城武器木材-33%</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 攻城工程技师、建筑学、工兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -3766,12 +3828,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
+          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、蝎式弩</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 重型蝎式弩、攻城工程技师、建筑学</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3843,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -3796,12 +3858,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>攻城武器木材-33%</t>
+          <t>骑兵对攻城武器的攻击力 +2</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 攻城工程技师、建筑学、工兵</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 攻城工程技师、建筑学、工兵</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3873,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -3826,12 +3888,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
+          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 重型蝎式弩、攻城工程技师、建筑学</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 化学、弹道学、工兵</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3903,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -3856,22 +3918,22 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>骑兵对攻城武器的攻击力 +2</t>
+          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 攻城工程技师、建筑学、工兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；蝎式弩科技树 8/9；缺 攻城工程技师</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -3886,12 +3948,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
+          <t>重装甲（攻城武器近战护甲+4）</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 化学、弹道学、工兵</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3963,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -3916,22 +3978,22 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；蝎式弩科技树 8/9；缺 攻城工程技师</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -3946,12 +4008,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>重装甲（攻城武器近战护甲+4）</t>
+          <t>攻城武器厂单位费用-15%</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -3961,27 +4023,27 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强蝎式弩</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「初始黄金+50」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；蝎式弩科技树 8/9；缺 重型蝎式弩</t>
         </is>
       </c>
     </row>
@@ -3991,7 +4053,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -4011,7 +4073,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
+          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「初始黄金+50」）</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4083,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -4041,7 +4103,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>防御文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4113,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -4071,7 +4133,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>防御文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4143,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -4101,7 +4163,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4173,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -4131,7 +4193,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4203,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -4161,7 +4223,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>步弓手文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「羊倌工作速度+25%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4233,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -4191,7 +4253,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>步弓手文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「羊倌工作速度+25%」）</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4263,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -4221,7 +4283,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4293,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -4251,7 +4313,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采果工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4323,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -4281,7 +4343,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4353,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -4311,7 +4373,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局有骡车」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4383,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -4341,7 +4403,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「每座TC食物+100」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4413,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -4371,7 +4433,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代速度+66%」）</t>
+          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「每座TC食物+100」）</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4443,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -4401,7 +4463,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代速度+66%」）</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4473,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -4431,7 +4493,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采果工存食+25%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4503,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -4461,7 +4523,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采果工存食+25%」）</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4533,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -4491,7 +4553,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局村民+1，食物-50」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4563,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -4521,7 +4583,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>象兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代TC产生2村民」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局村民+1，食物-50」）</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4593,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -4551,7 +4613,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4623,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -4581,7 +4643,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4653,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -4611,7 +4673,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4683,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -4641,7 +4703,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5437,101 +5499,141 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>① 只看直接作用于蝎式弩本体、或其前置/费用/产出的条目；</t>
+          <t>本表按用户打法口径分四个阶段排序：先加强要玩的主流派兵种，再减它的资源消耗，最后才补资源效率。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="11" t="inlineStr"/>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>① 阶段 1 · 本体强化</t>
+        </is>
+      </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>② 泛用条目与兵种类一律剔除（放进「与弩车流无关·可跳过」）；</t>
+          <t>直接加强蝎式弩本体的条目（攻击/护甲/生命/攻速/射程/移速/回血/数量/生产训练速度/解锁升级等）。这一档最优先。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="11" t="inlineStr"/>
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>② 阶段 2 · 减费用</t>
+        </is>
+      </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
+          <t>降低该兵种及同系兵种（攻城武器厂单位）生产所需资源的条目：费用/成本 -N%、升级免费、用其它资源替代。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="11" t="inlineStr"/>
-      <c r="B15" s="11" t="inlineStr"/>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>③ 阶段 3 · 资源效率</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>采集/产出/携带/贸易/人口/经济科技等让主流派更快成型的条目。</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>未验证项</t>
+          <t>④ 阶段 4 · 其他相关</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
+          <t>其余与本流派相关、但不属于上述三类的条目。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>★ 最重要的一条：别买重复</t>
-        </is>
-      </c>
+      <c r="A17" s="11" t="inlineStr"/>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
+          <t>同阶段内按「人工权威顺序（实战强度）」再排；泛用条目与兵种类一律剔除（放进「与弩车流无关·可跳过」）。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="11" t="inlineStr"/>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
-        </is>
-      </c>
+      <c r="B18" s="11" t="inlineStr"/>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>数据来源</t>
+          <t>未验证项</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="11" t="inlineStr"/>
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>★ 最重要的一条：别买重复</t>
+        </is>
+      </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>整理</t>
-        </is>
-      </c>
+      <c r="A21" s="11" t="inlineStr"/>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>By RemonBo；本表由 DSH 生成。</t>
+          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="11" t="inlineStr"/>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>整理</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>By RemonBo；本表由 DSH 生成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 弩车流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 弩车流最优研究顺序 By RemonBo.xlsx
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·蝎式弩本体强化'!$A$1:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·蝎式弩本体强化'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·蝎式弩本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与弩车流无关·可跳过'!$A$1:$D$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与弩车流无关·可跳过'!$A$1:$D$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与弩车流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
@@ -579,7 +579,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>蝎式弩黄金-50%；弩炮（蝎式弩攻速+33%；箭船系攻+2）；降低蝎式弩的最小射程</t>
+          <t>弩炮（蝎式弩攻速+33%；箭船系攻+2）；降低蝎式弩的最小射程</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -592,13 +592,13 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>萨拉森（备选）</t>
+          <t>凯尔特（备选）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、建筑学</t>
+          <t>备选：阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -606,13 +606,13 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>凯尔特（备选）</t>
+          <t>丹麦人（备选）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 建筑学、工兵</t>
         </is>
       </c>
     </row>
@@ -648,13 +648,13 @@
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>丹麦人（备选）</t>
+          <t>埃塞俄比亚（备选）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 建筑学、工兵</t>
+          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
         </is>
       </c>
     </row>
@@ -662,13 +662,13 @@
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚（备选）</t>
+          <t>蒙古（备选）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
+          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -704,13 +704,13 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>蒙古（备选）</t>
+          <t>蜀（备选）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、蝎式弩</t>
         </is>
       </c>
     </row>
@@ -718,13 +718,13 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>蜀（备选）</t>
+          <t>库曼（备选）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、蝎式弩</t>
+          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 重型蝎式弩、攻城工程技师、建筑学</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -795,7 +795,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>配重块（巨型投石机/投石车系攻+15%）</t>
+          <t>攻城武器攻速+25%；凯尔特狂暴（攻城武器生命+40%）；攻城武器厂的生产速度 +20%</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、建筑学</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>攻城武器攻速+25%；凯尔特狂暴（攻城武器生命+40%）；攻城武器厂的生产速度 +20%</t>
+          <t>攻城武器的视野 +2</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -845,17 +845,17 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 建筑学、工兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>兵营/攻城武器厂黄金升级-66%；北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）；攻城武器的视野 +2</t>
+          <t>扭绞机（攻城武器厂单位爆炸伤害范围提升）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 建筑学、工兵</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>扭绞机（攻城武器厂单位爆炸伤害范围提升）</t>
+          <t>操练（攻城武器厂单位移速+50%）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -925,17 +925,17 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>操练（攻城武器厂单位移速+50%）</t>
+          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、蝎式弩</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -955,17 +955,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
+          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>封建时代起</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、蝎式弩</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 重型蝎式弩、攻城工程技师、建筑学</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>攻城武器木材-33%</t>
+          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 攻城工程技师、建筑学、工兵</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 化学、弹道学、工兵</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1015,17 +1015,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
+          <t>重装甲（攻城武器近战护甲+4）</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>封建时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 重型蝎式弩、攻城工程技师、建筑学</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>骑兵对攻城武器的攻击力 +2</t>
+          <t>攻城武器木材-33%</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 攻城工程技师、建筑学、工兵</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 攻城工程技师、建筑学、工兵</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
+          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 化学、弹道学、工兵</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1105,17 +1105,17 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>攻城武器厂单位费用-15%</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；蝎式弩科技树 8/9；缺 攻城工程技师</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>重装甲（攻城武器近战护甲+4）</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1145,102 +1145,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>攻城武器厂单位费用-15%</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>所有单位黄金费用-20%</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
           <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；蝎式弩科技树 8/9；缺 重型蝎式弩</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:F13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1252,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1302,17 +1212,17 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>蝎式弩黄金-50%</t>
+          <t>弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -1329,17 +1239,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>弩炮（蝎式弩攻速+33%；箭船系攻+2）</t>
+          <t>降低蝎式弩的最小射程</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>射程提升</t>
         </is>
       </c>
     </row>
@@ -1351,22 +1261,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>降低蝎式弩的最小射程</t>
+          <t>双箭弩（重弩战象/蝎式弩可多发一枚弩箭）</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
         </is>
       </c>
     </row>
@@ -1383,17 +1293,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>双箭弩（重弩战象/蝎式弩可多发一枚弩箭）</t>
+          <t>蝎式弩射程 +1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
+          <t>射程提升</t>
         </is>
       </c>
     </row>
@@ -1405,49 +1315,49 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>蝎式弩射程 +1</t>
+          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>火箭术（弩炮/火箭推车/楼船攻+25%；楼船可发火箭）</t>
+          <t>攻城武器攻速+25%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1369,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>配重块（巨型投石机/投石车系攻+15%）</t>
+          <t>凯尔特狂暴（攻城武器生命+40%）</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1474,7 +1384,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -1491,17 +1401,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>攻城武器攻速+25%</t>
+          <t>攻城武器厂的生产速度 +20%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>研究/生产速度提升，科技与产能来得更快</t>
         </is>
       </c>
     </row>
@@ -1513,22 +1423,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>凯尔特狂暴（攻城武器生命+40%）</t>
+          <t>攻城武器的视野 +2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>视野提升</t>
         </is>
       </c>
     </row>
@@ -1540,22 +1450,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>攻城武器厂的生产速度 +20%</t>
+          <t>扭绞机（攻城武器厂单位爆炸伤害范围提升）</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>研究/生产速度提升，科技与产能来得更快</t>
+          <t>爆炸/溅射范围提升</t>
         </is>
       </c>
     </row>
@@ -1567,324 +1477,135 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>兵营/攻城武器厂黄金升级-66%</t>
+          <t>操练（攻城武器厂单位移速+50%）</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>马其顿人</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>条顿</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>重装甲（攻城武器近战护甲+4）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>射程提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>攻城武器的视野 +2</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>视野提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>扭绞机（攻城武器厂单位爆炸伤害范围提升）</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>爆炸/溅射范围提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>蒙古</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>操练（攻城武器厂单位移速+50%）</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>攻城武器木材-33%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>库曼</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>提前解锁，抢一个时代的节奏</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>魏</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>骑兵对攻城武器的攻击力 +2</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>马其顿人</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
           <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>减少受到的伤害，正面更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>条顿</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>重装甲（攻城武器近战护甲+4）</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E23"/>
+  <autoFilter ref="A1:E16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1896,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1934,19 +1655,19 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
+          <t>蝎式弩黄金-50%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1961,19 +1682,19 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>攻城武器厂单位费用-15%</t>
+          <t>兵营/攻城武器厂黄金升级-66%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1995,27 +1716,108 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>攻城武器木材-33%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>攻城武器厂单位费用-15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>葡萄牙</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>所有单位黄金费用-20%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2027,7 +1829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2149,12 +1951,12 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2164,19 +1966,19 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「初始木材/食物+50」）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -2186,19 +1988,19 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>步弓手文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -2208,19 +2010,19 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>步弓手文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「羊倌工作速度+25%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>骑射手文明</t>
+          <t>步弓手文明</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -2230,19 +2032,19 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>步弓手文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「羊倌工作速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>骑射手文明</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -2252,19 +2054,19 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>防御和海军文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -2274,19 +2076,19 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采果工速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>防御和海军文明</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -2296,19 +2098,19 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>防御和骑兵文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2318,19 +2120,19 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局有骡车」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明</t>
+          <t>防御和骑兵文明</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -2340,19 +2142,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「每座TC食物+100」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>海军文明</t>
+          <t>骑兵和僧侣文明</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -2362,19 +2164,19 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代速度+66%」）</t>
+          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「每座TC食物+100」）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>海军文明</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -2384,19 +2186,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代速度+66%」）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>骑兵与反制单位文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -2406,19 +2208,19 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采果工存食+25%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>骑兵与反制单位文明</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2428,19 +2230,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采果工存食+25%」）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>弓兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2450,19 +2252,19 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局村民+1，食物-50」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>象兵和海军文明</t>
+          <t>弓兵文明</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2472,19 +2274,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>象兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代TC产生2村民」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局村民+1，食物-50」）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>象兵和海军文明</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2494,19 +2296,19 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2516,19 +2318,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>骑兵和火药文明</t>
+          <t>弓兵与僧侣文明</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2538,19 +2340,19 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵和火药文明</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2560,19 +2362,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牧场取代农田」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2582,19 +2384,19 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局2果树丛」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牧场取代农田」）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>骑兵和骆驼文明</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2604,19 +2406,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局2果树丛」）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2626,19 +2428,19 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2648,19 +2450,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局每种资源+25」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>火药文明</t>
+          <t>骆驼和海军文明</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2670,19 +2472,19 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>骆驼和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「市场贸易税仅5%」）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>弓兵与步兵文明</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2692,19 +2494,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局每种资源+25」）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>火药文明</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2714,19 +2516,19 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「独轮推车/手推车免费」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>骑兵和海军文明</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2736,19 +2538,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2758,19 +2560,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2780,19 +2582,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「初始石料+100」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2802,19 +2604,19 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2824,19 +2626,19 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>弓兵和海军文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2846,19 +2648,19 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代费用-15%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2868,19 +2670,19 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2890,19 +2692,19 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「房屋/聚落人口+5」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>弓兵文明</t>
+          <t>弓兵和海军文明</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2912,19 +2714,19 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局显示敌方TC」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明</t>
+          <t>骆驼和火药文明</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2934,19 +2736,19 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「造船厂工作速度+15%」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2956,19 +2758,19 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采石村民缓慢获食」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「房屋/聚落人口+5」）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>弓兵文明</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2978,19 +2780,19 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局显示敌方TC」）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>弓兵和骑兵文明</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3000,34 +2802,100 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
+          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「造船厂工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>普鲁人</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>弓兵和象兵文明</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>无一条直接加强蝎式弩</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采石村民缓慢获食」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>步兵文明</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>无一条直接加强蝎式弩</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>步兵文明</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>无一条直接加强蝎式弩</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t>雅典</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>步兵和海军文明</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强蝎式弩</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>无一条直接加强蝎式弩</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D45"/>
+  <autoFilter ref="A1:D48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3157,22 +3025,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>配重块（巨型投石机/投石车系攻+15%）</t>
+          <t>攻城武器攻速+25%；凯尔特狂暴（攻城武器生命+40%）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 7/9。缺：重型蝎式弩、建筑学</t>
+          <t>原生条目 3 条（强 0）；蝎式弩科技树 8/9。缺：建筑学</t>
         </is>
       </c>
     </row>
@@ -3182,47 +3050,47 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>攻城武器攻速+25%；凯尔特狂暴（攻城武器生命+40%）</t>
+          <t>兵营/攻城武器厂黄金升级-66%；攻城武器的视野 +2</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 0）；蝎式弩科技树 8/9。缺：建筑学</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+          <t>原生条目 2 条（强 0）；蝎式弩科技树 7/9。缺：建筑学、工兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>兵营/攻城武器厂黄金升级-66%；北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）</t>
+          <t>扭绞机（攻城武器厂单位爆炸伤害范围提升）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 0）；蝎式弩科技树 7/9。缺：建筑学、工兵</t>
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 9/9。科技树无缺项</t>
         </is>
       </c>
     </row>
@@ -3232,22 +3100,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>扭绞机（攻城武器厂单位爆炸伤害范围提升）</t>
+          <t>操练（攻城武器厂单位移速+50%）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 9/9。科技树无缺项</t>
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 8/9。缺：建筑学</t>
         </is>
       </c>
     </row>
@@ -3257,47 +3125,47 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>操练（攻城武器厂单位移速+50%）</t>
+          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 8/9。缺：建筑学</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 7/9。缺：重型蝎式弩、蝎式弩</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
+          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 7/9。缺：重型蝎式弩、蝎式弩</t>
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 6/9。缺：重型蝎式弩、攻城工程技师、建筑学</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3175,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3317,37 +3185,37 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>攻城武器木材-33%</t>
+          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 6/9。缺：攻城工程技师、建筑学、工兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 6/9。缺：化学、弹道学、工兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
+          <t>重装甲（攻城武器近战护甲+4）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 6/9。缺：重型蝎式弩、攻城工程技师、建筑学</t>
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 8/9。缺：建筑学</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3225,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3367,7 +3235,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>骑兵对攻城武器的攻击力 +2</t>
+          <t>攻城武器木材-33%</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -3382,22 +3250,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
+          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 6/9。缺：化学、弹道学、工兵</t>
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 9/9。科技树无缺项</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3275,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3417,12 +3285,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>攻城武器厂单位费用-15%</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 8/9。缺：攻城工程技师</t>
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 8/9。缺：建筑学</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3300,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3442,12 +3310,12 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>重装甲（攻城武器近战护甲+4）</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；蝎式弩科技树 8/9。缺：建筑学</t>
+          <t>原生条目 1 条（强 0）；蝎式弩科技树 8/9。缺：重型蝎式弩</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3396,7 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>蝎式弩黄金-50%；弩炮（蝎式弩攻速+33%；箭船系攻+2）；降低蝎式弩的最小射程</t>
+          <t>弩炮（蝎式弩攻速+33%；箭船系攻+2）；降低蝎式弩的最小射程</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -3603,7 +3471,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -3618,12 +3486,12 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>配重块（巨型投石机/投石车系攻+15%）</t>
+          <t>攻城武器攻速+25%；凯尔特狂暴（攻城武器生命+40%）；攻城武器厂的生产速度 +20%</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、建筑学</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3501,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -3648,22 +3516,22 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>攻城武器攻速+25%；凯尔特狂暴（攻城武器生命+40%）；攻城武器厂的生产速度 +20%</t>
+          <t>攻城武器的视野 +2</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 建筑学、工兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3678,12 +3546,12 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>兵营/攻城武器厂黄金升级-66%；北方人之怒（投石车系/大型投石战舰射程+1；攻城武器/攻城战舰对建筑攻+40%）；攻城武器的视野 +2</t>
+          <t>扭绞机（攻城武器厂单位爆炸伤害范围提升）</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 建筑学、工兵</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3561,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3708,12 +3576,12 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>扭绞机（攻城武器厂单位爆炸伤害范围提升）</t>
+          <t>操练（攻城武器厂单位移速+50%）</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3591,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3738,12 +3606,12 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>操练（攻城武器厂单位移速+50%）</t>
+          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、蝎式弩</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3621,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -3768,12 +3636,12 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>攻城武器/攻城战舰城堡/帝王移速+10/15%</t>
+          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 7/9；缺 重型蝎式弩、蝎式弩</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 重型蝎式弩、攻城工程技师、建筑学</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3651,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -3798,12 +3666,12 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>攻城武器木材-33%</t>
+          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 攻城工程技师、建筑学、工兵</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 化学、弹道学、工兵</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3681,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -3828,12 +3696,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>封建可用攻城武器厂/攻城锤，城堡可用中型冲车</t>
+          <t>重装甲（攻城武器近战护甲+4）</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 重型蝎式弩、攻城工程技师、建筑学</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3711,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -3858,12 +3726,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>骑兵对攻城武器的攻击力 +2</t>
+          <t>攻城武器木材-33%</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 攻城工程技师、建筑学、工兵</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 攻城工程技师、建筑学、工兵</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3741,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -3888,12 +3756,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>攻城武器对建筑远程护甲+1，伤害+30%</t>
+          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 6/9；缺 化学、弹道学、工兵</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3771,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -3918,12 +3786,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>堡垒（城堡攻+4，对冲车/步兵攻+3，额外受伤-25%）</t>
+          <t>攻城武器厂单位费用-15%</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；蝎式弩科技树 8/9；缺 攻城工程技师</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3801,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -3948,12 +3816,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重装甲（攻城武器近战护甲+4）</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；蝎式弩科技树 8/9；缺 重型蝎式弩</t>
         </is>
       </c>
     </row>
@@ -3963,27 +3831,27 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>阿兹特克</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2000 金</t>
+          <t>不建议</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>铁匠铺/攻城武器厂科技食物费用-50%</t>
+          <t>无一条直接加强蝎式弩</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 9/9（无缺项）</t>
+          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「初始黄金+50」）</t>
         </is>
       </c>
     </row>
@@ -3993,27 +3861,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2000 金</t>
+          <t>不建议</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>攻城武器厂单位费用-15%</t>
+          <t>无一条直接加强蝎式弩</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；蝎式弩科技树 8/9；缺 建筑学</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
         </is>
       </c>
     </row>
@@ -4023,27 +3891,27 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2000 金</t>
+          <t>不建议</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>所有单位黄金费用-20%</t>
+          <t>无一条直接加强蝎式弩</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；蝎式弩科技树 8/9；缺 重型蝎式弩</t>
+          <t>防御文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
         </is>
       </c>
     </row>
@@ -4053,7 +3921,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -4073,7 +3941,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「初始黄金+50」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -4083,7 +3951,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -4103,7 +3971,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「初始木材/食物+50」）</t>
         </is>
       </c>
     </row>
@@ -4113,7 +3981,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -4133,7 +4001,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>防御文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4011,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -4163,7 +4031,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4041,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -4193,7 +4061,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>步弓手文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「羊倌工作速度+25%」）</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4071,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -4223,7 +4091,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4101,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -4253,7 +4121,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>步弓手文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「羊倌工作速度+25%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采果工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4131,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -4283,7 +4151,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4161,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -4313,7 +4181,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4191,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -4343,7 +4211,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4221,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -4373,7 +4241,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「每座TC食物+100」）</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4251,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -4403,7 +4271,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局有骡车」）</t>
+          <t>海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代速度+66%」）</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4281,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -4433,7 +4301,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「每座TC食物+100」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4311,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -4463,7 +4331,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代速度+66%」）</t>
+          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采果工存食+25%」）</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4341,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -4493,7 +4361,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4371,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -4523,7 +4391,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「采果工存食+25%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局村民+1，食物-50」）</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4401,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -4553,7 +4421,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4431,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -4583,7 +4451,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局村民+1，食物-50」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4461,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -4613,7 +4481,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>象兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代TC产生2村民」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4491,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -4643,7 +4511,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4521,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -4673,7 +4541,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牧场取代农田」）</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4551,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -4703,7 +4571,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局2果树丛」）</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4581,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -4733,7 +4601,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牧场取代农田」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4611,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -4763,7 +4631,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局2果树丛」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4641,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -4793,7 +4661,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>骆驼和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「市场贸易税仅5%」）</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4671,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
@@ -4823,7 +4691,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局每种资源+25」）</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4701,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
@@ -4853,7 +4721,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「开局每种资源+25」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4731,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
@@ -4883,7 +4751,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4761,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
@@ -4913,7 +4781,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4791,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
@@ -4943,7 +4811,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「独轮推车/手推车免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于蝎式弩。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
         </is>
       </c>
     </row>
